--- a/2025_06_22_List_of_Riyadh_dsitricts_stripped_of_population.xlsx
+++ b/2025_06_22_List_of_Riyadh_dsitricts_stripped_of_population.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48147536e8c31483/Distance between dental clinics and metro and bus stations/Manuscript/Submission to JDR/Github/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48147536e8c31483/Claude code projects/Simulation of transit access to dental facilities/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="448" documentId="8_{AF16C976-66B7-4B31-B03D-938CB0FC0130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE638EA9-25EE-4319-A592-B7B3253838F6}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="8_{AF16C976-66B7-4B31-B03D-938CB0FC0130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1BBCF4B-F0EB-469A-B4FE-69C40A6EE39B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{5B5C95F6-513A-40FF-8ABC-E19E602B4C04}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1859" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="412">
   <si>
     <t>Region</t>
   </si>
@@ -1270,9 +1270,6 @@
   </si>
   <si>
     <t>New Region</t>
-  </si>
-  <si>
-    <t>Population</t>
   </si>
   <si>
     <t>Includes Dhahyat Al Khuzam</t>
@@ -7065,13 +7062,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C606D6CE-ADF0-4B11-9CC1-0A29157D5BE0}">
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="9" width="16.6328125" customWidth="1"/>
+    <col min="1" max="8" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>250</v>
       </c>
@@ -7096,11 +7093,8 @@
       <c r="H1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -7119,11 +7113,8 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2">
-        <v>35507</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -7142,11 +7133,8 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
-      <c r="I3">
-        <v>49965</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -7165,11 +7153,8 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4">
-        <v>42594</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -7188,11 +7173,8 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5">
-        <v>39391</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -7211,11 +7193,8 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6">
-        <v>16460</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -7234,11 +7213,8 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7">
-        <v>27415</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -7257,11 +7233,8 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8">
-        <v>20338</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -7280,11 +7253,8 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9">
-        <v>34511</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -7303,11 +7273,8 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10">
-        <v>17697</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -7328,11 +7295,8 @@
       <c r="H11" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="I11">
-        <v>26336</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -7351,11 +7315,8 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12">
-        <v>39241</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -7374,11 +7335,8 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="I13">
-        <v>55187</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -7397,11 +7355,8 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14">
-        <v>90252</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -7420,11 +7375,8 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-      <c r="I15">
-        <v>118753</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -7443,11 +7395,8 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16">
-        <v>70591</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -7466,11 +7415,8 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-      <c r="I17">
-        <v>18684</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -7489,11 +7435,8 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18">
-        <v>93066</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -7512,11 +7455,8 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19">
-        <v>65790</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -7535,11 +7475,8 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20">
-        <v>30972</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -7558,11 +7495,8 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21">
-        <v>58068</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -7581,11 +7515,8 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22">
-        <v>15526</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -7604,11 +7535,8 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="I23">
-        <v>20513</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -7627,11 +7555,8 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-      <c r="I24">
-        <v>34355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -7650,11 +7575,8 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25">
-        <v>27452</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -7673,11 +7595,8 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
-      <c r="I26">
-        <v>22125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -7696,11 +7615,8 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
-      <c r="I27">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -7719,11 +7635,8 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
-      <c r="I28">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -7742,11 +7655,8 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
-      <c r="I29">
-        <v>6442</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -7765,11 +7675,8 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
-      <c r="I30">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -7788,11 +7695,8 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31">
-        <v>10586</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -7811,11 +7715,8 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -7834,11 +7735,8 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33">
-        <v>25580</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -7857,11 +7755,8 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34">
-        <v>3451</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -7880,11 +7775,8 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35">
-        <v>2717</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -7903,11 +7795,8 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36">
-        <v>3862</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -7926,11 +7815,8 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -7949,11 +7835,8 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
-      <c r="I38">
-        <v>11461</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -7972,11 +7855,8 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="I39">
-        <v>51221</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -7995,11 +7875,8 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
-      <c r="I40">
-        <v>28975</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -8018,11 +7895,8 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
-      <c r="I41">
-        <v>38382</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -8041,11 +7915,8 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42">
-        <v>39942</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -8064,11 +7935,8 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
-      <c r="I43">
-        <v>68835</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -8087,11 +7955,8 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44">
-        <v>8142</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -8110,11 +7975,8 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45">
-        <v>22453</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>118</v>
       </c>
@@ -8133,11 +7995,8 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
-      <c r="I46">
-        <v>29547</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>119</v>
       </c>
@@ -8156,11 +8015,8 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
-      <c r="I47">
-        <v>21720</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>120</v>
       </c>
@@ -8179,11 +8035,8 @@
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
-      <c r="I48">
-        <v>14600</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>121</v>
       </c>
@@ -8202,11 +8055,8 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
-      <c r="I49">
-        <v>9627</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>122</v>
       </c>
@@ -8225,11 +8075,8 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
-      <c r="I50">
-        <v>15932</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>123</v>
       </c>
@@ -8248,11 +8095,8 @@
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
-      <c r="I51">
-        <v>34372</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>124</v>
       </c>
@@ -8271,11 +8115,8 @@
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
-      <c r="I52">
-        <v>37663</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>125</v>
       </c>
@@ -8294,11 +8135,8 @@
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
-      <c r="I53">
-        <v>6160</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>126</v>
       </c>
@@ -8317,11 +8155,8 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
-      <c r="I54">
-        <v>8127</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>127</v>
       </c>
@@ -8340,11 +8175,8 @@
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
-      <c r="I55">
-        <v>16529</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>128</v>
       </c>
@@ -8363,11 +8195,8 @@
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
-      <c r="I56">
-        <v>6192</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>129</v>
       </c>
@@ -8386,11 +8215,8 @@
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
-      <c r="I57">
-        <v>13892</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>130</v>
       </c>
@@ -8409,11 +8235,8 @@
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
-      <c r="I58">
-        <v>6897</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>131</v>
       </c>
@@ -8432,11 +8255,8 @@
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
-      <c r="I59">
-        <v>23867</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>132</v>
       </c>
@@ -8455,11 +8275,8 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
-      <c r="I60">
-        <v>32090</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>133</v>
       </c>
@@ -8478,11 +8295,8 @@
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
-      <c r="I61">
-        <v>24858</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>142</v>
       </c>
@@ -8501,11 +8315,8 @@
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
-      <c r="I62">
-        <v>30180</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>145</v>
       </c>
@@ -8524,11 +8335,8 @@
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
-      <c r="I63">
-        <v>11518</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>146</v>
       </c>
@@ -8547,11 +8355,8 @@
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
-      <c r="I64">
-        <v>6402</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>151</v>
       </c>
@@ -8570,11 +8375,8 @@
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
-      <c r="I65">
-        <v>16493</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>152</v>
       </c>
@@ -8593,11 +8395,8 @@
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
-      <c r="I66">
-        <v>2756</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>180</v>
       </c>
@@ -8616,11 +8415,8 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="5"/>
-      <c r="I67">
-        <v>18806</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>181</v>
       </c>
@@ -8639,11 +8435,8 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="5"/>
-      <c r="I68">
-        <v>13007</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>182</v>
       </c>
@@ -8662,11 +8455,8 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="5"/>
-      <c r="I69">
-        <v>58269</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>183</v>
       </c>
@@ -8685,11 +8475,8 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="5"/>
-      <c r="I70">
-        <v>3888</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>187</v>
       </c>
@@ -8708,11 +8495,8 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="5"/>
-      <c r="I71">
-        <v>15164</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>45</v>
       </c>
@@ -8731,11 +8515,8 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
-      <c r="I72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>46</v>
       </c>
@@ -8754,11 +8535,8 @@
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
-      <c r="I73">
-        <v>120695</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>47</v>
       </c>
@@ -8777,11 +8555,8 @@
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
-      <c r="I74">
-        <v>13426</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>48</v>
       </c>
@@ -8800,11 +8575,8 @@
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
-      <c r="I75">
-        <v>22592</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>49</v>
       </c>
@@ -8823,11 +8595,8 @@
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
-      <c r="I76">
-        <v>58777</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>50</v>
       </c>
@@ -8846,11 +8615,8 @@
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
-      <c r="I77">
-        <v>12302</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>51</v>
       </c>
@@ -8869,11 +8635,8 @@
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
-      <c r="I78">
-        <v>70875</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>52</v>
       </c>
@@ -8892,11 +8655,8 @@
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
-      <c r="I79">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>63</v>
       </c>
@@ -8915,11 +8675,8 @@
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
-      <c r="I80">
-        <v>99091</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>64</v>
       </c>
@@ -8938,11 +8695,8 @@
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
-      <c r="I81">
-        <v>98961</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>65</v>
       </c>
@@ -8961,11 +8715,8 @@
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
-      <c r="I82">
-        <v>96370</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>66</v>
       </c>
@@ -8984,11 +8735,8 @@
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
-      <c r="I83">
-        <v>53967</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>67</v>
       </c>
@@ -9007,11 +8755,8 @@
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
-      <c r="I84">
-        <v>34630</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>68</v>
       </c>
@@ -9030,11 +8775,8 @@
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
-      <c r="I85">
-        <v>53554</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>69</v>
       </c>
@@ -9053,11 +8795,8 @@
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
-      <c r="I86">
-        <v>41637</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>70</v>
       </c>
@@ -9076,11 +8815,8 @@
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
-      <c r="I87">
-        <v>99115</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>71</v>
       </c>
@@ -9099,11 +8835,8 @@
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
-      <c r="I88">
-        <v>100677</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>72</v>
       </c>
@@ -9122,11 +8855,8 @@
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
-      <c r="I89">
-        <v>33304</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>73</v>
       </c>
@@ -9145,11 +8875,8 @@
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
-      <c r="I90">
-        <v>29591</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>74</v>
       </c>
@@ -9168,11 +8895,8 @@
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
-      <c r="I91">
-        <v>87548</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>75</v>
       </c>
@@ -9191,11 +8915,8 @@
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
-      <c r="I92">
-        <v>130215</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>76</v>
       </c>
@@ -9214,11 +8935,8 @@
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
-      <c r="I93">
-        <v>141144</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>156</v>
       </c>
@@ -9237,11 +8955,8 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="5"/>
-      <c r="I94">
-        <v>43383</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>158</v>
       </c>
@@ -9262,11 +8977,8 @@
       <c r="H95" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="I95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>78</v>
       </c>
@@ -9285,11 +8997,8 @@
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
-      <c r="I96">
-        <v>24782</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>79</v>
       </c>
@@ -9308,11 +9017,8 @@
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
-      <c r="I97">
-        <v>49438</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>80</v>
       </c>
@@ -9331,11 +9037,8 @@
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
-      <c r="I98">
-        <v>21308</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>81</v>
       </c>
@@ -9354,11 +9057,8 @@
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
-      <c r="I99">
-        <v>53471</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>82</v>
       </c>
@@ -9377,11 +9077,8 @@
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
-      <c r="I100">
-        <v>35795</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>83</v>
       </c>
@@ -9400,11 +9097,8 @@
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
-      <c r="I101">
-        <v>87931</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>84</v>
       </c>
@@ -9423,11 +9117,8 @@
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
-      <c r="I102">
-        <v>52135</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>85</v>
       </c>
@@ -9446,11 +9137,8 @@
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
-      <c r="I103">
-        <v>35054</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>86</v>
       </c>
@@ -9469,11 +9157,8 @@
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
-      <c r="I104">
-        <v>19017</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>87</v>
       </c>
@@ -9492,11 +9177,8 @@
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
-      <c r="I105">
-        <v>107229</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>88</v>
       </c>
@@ -9515,11 +9197,8 @@
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
-      <c r="I106">
-        <v>6241</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>89</v>
       </c>
@@ -9538,11 +9217,8 @@
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
-      <c r="I107">
-        <v>82800</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>90</v>
       </c>
@@ -9561,11 +9237,8 @@
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
-      <c r="I108">
-        <v>81528</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>91</v>
       </c>
@@ -9584,11 +9257,8 @@
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
-      <c r="I109">
-        <v>39300</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>92</v>
       </c>
@@ -9607,11 +9277,8 @@
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
-      <c r="I110">
-        <v>42122</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>93</v>
       </c>
@@ -9630,11 +9297,8 @@
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
-      <c r="I111">
-        <v>10889</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>94</v>
       </c>
@@ -9653,11 +9317,8 @@
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
-      <c r="I112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>184</v>
       </c>
@@ -9676,11 +9337,8 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="5"/>
-      <c r="I113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>185</v>
       </c>
@@ -9699,13 +9357,10 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
       <c r="H114" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="I114">
-        <v>17031</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>53</v>
       </c>
@@ -9724,11 +9379,8 @@
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
-      <c r="I115">
-        <v>139943</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>54</v>
       </c>
@@ -9747,11 +9399,8 @@
       <c r="F116" s="5"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
-      <c r="I116">
-        <v>159949</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>55</v>
       </c>
@@ -9770,11 +9419,8 @@
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
-      <c r="I117">
-        <v>26584</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>56</v>
       </c>
@@ -9793,11 +9439,8 @@
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
-      <c r="I118">
-        <v>83187</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>57</v>
       </c>
@@ -9816,11 +9459,8 @@
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
-      <c r="I119">
-        <v>58107</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>58</v>
       </c>
@@ -9839,11 +9479,8 @@
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
-      <c r="I120">
-        <v>39842</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>59</v>
       </c>
@@ -9864,11 +9501,8 @@
       <c r="H121" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="I121">
-        <v>42558</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>60</v>
       </c>
@@ -9887,11 +9521,8 @@
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
-      <c r="I122">
-        <v>38492</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>61</v>
       </c>
@@ -9910,11 +9541,8 @@
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
-      <c r="I123">
-        <v>57209</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>62</v>
       </c>
@@ -9933,11 +9561,8 @@
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
-      <c r="I124">
-        <v>50079</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>77</v>
       </c>
@@ -9956,11 +9581,8 @@
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
-      <c r="I125">
-        <v>6279</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>96</v>
       </c>
@@ -9979,11 +9601,8 @@
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
-      <c r="I126">
-        <v>175897</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>97</v>
       </c>
@@ -10002,11 +9621,8 @@
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
-      <c r="I127">
-        <v>157909</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>98</v>
       </c>
@@ -10025,11 +9641,8 @@
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
-      <c r="I128">
-        <v>2617</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>99</v>
       </c>
@@ -10048,11 +9661,8 @@
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
-      <c r="I129">
-        <v>14321</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>100</v>
       </c>
@@ -10071,11 +9681,8 @@
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
-      <c r="I130">
-        <v>70513</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>101</v>
       </c>
@@ -10094,11 +9701,8 @@
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
-      <c r="I131">
-        <v>25114</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>102</v>
       </c>
@@ -10117,11 +9721,8 @@
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
-      <c r="I132">
-        <v>21117</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>103</v>
       </c>
@@ -10140,11 +9741,8 @@
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
-      <c r="I133">
-        <v>17743</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>104</v>
       </c>
@@ -10163,11 +9761,8 @@
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
-      <c r="I134">
-        <v>38410</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>105</v>
       </c>
@@ -10186,11 +9781,8 @@
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
-      <c r="I135">
-        <v>20287</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>106</v>
       </c>
@@ -10209,11 +9801,8 @@
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
-      <c r="I136">
-        <v>116151</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>107</v>
       </c>
@@ -10232,11 +9821,8 @@
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
-      <c r="I137">
-        <v>14051</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>108</v>
       </c>
@@ -10255,11 +9841,8 @@
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
       <c r="H138" s="5"/>
-      <c r="I138">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>109</v>
       </c>
@@ -10278,11 +9861,8 @@
       <c r="F139" s="5"/>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
-      <c r="I139">
-        <v>5490</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>110</v>
       </c>
@@ -10301,11 +9881,8 @@
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
-      <c r="I140">
-        <v>7162</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>111</v>
       </c>
@@ -10324,11 +9901,8 @@
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
-      <c r="I141">
-        <v>102196</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>112</v>
       </c>
@@ -10347,11 +9921,8 @@
       <c r="F142" s="5"/>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
-      <c r="I142">
-        <v>9140</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>113</v>
       </c>
@@ -10370,11 +9941,8 @@
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
-      <c r="I143">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>114</v>
       </c>
@@ -10393,11 +9961,8 @@
       <c r="F144" s="5"/>
       <c r="G144" s="5"/>
       <c r="H144" s="5"/>
-      <c r="I144">
-        <v>8156</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>115</v>
       </c>
@@ -10416,11 +9981,8 @@
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
-      <c r="I145">
-        <v>32566</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>116</v>
       </c>
@@ -10439,11 +10001,8 @@
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
-      <c r="I146">
-        <v>35362</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>117</v>
       </c>
@@ -10462,11 +10021,8 @@
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
-      <c r="I147">
-        <v>11288</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>95</v>
       </c>
@@ -10487,11 +10043,8 @@
       <c r="H148" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="I148">
-        <v>8936</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>134</v>
       </c>
@@ -10510,11 +10063,8 @@
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
-      <c r="I149">
-        <v>23951</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>135</v>
       </c>
@@ -10533,11 +10083,8 @@
       <c r="F150" s="5"/>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
-      <c r="I150">
-        <v>58475</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>136</v>
       </c>
@@ -10556,11 +10103,8 @@
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
-      <c r="I151">
-        <v>39342</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>137</v>
       </c>
@@ -10579,11 +10123,8 @@
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
-      <c r="I152">
-        <v>17510</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>138</v>
       </c>
@@ -10602,11 +10143,8 @@
       <c r="F153" s="5"/>
       <c r="G153" s="5"/>
       <c r="H153" s="5"/>
-      <c r="I153">
-        <v>47109</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>139</v>
       </c>
@@ -10625,11 +10163,8 @@
       <c r="F154" s="5"/>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
-      <c r="I154">
-        <v>42356</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>140</v>
       </c>
@@ -10648,11 +10183,8 @@
       <c r="F155" s="5"/>
       <c r="G155" s="5"/>
       <c r="H155" s="5"/>
-      <c r="I155">
-        <v>104688</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>141</v>
       </c>
@@ -10671,11 +10203,8 @@
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
-      <c r="I156">
-        <v>49357</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>143</v>
       </c>
@@ -10694,11 +10223,8 @@
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
       <c r="H157" s="5"/>
-      <c r="I157">
-        <v>52233</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>144</v>
       </c>
@@ -10717,11 +10243,8 @@
       <c r="F158" s="5"/>
       <c r="G158" s="5"/>
       <c r="H158" s="5"/>
-      <c r="I158">
-        <v>9146</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>147</v>
       </c>
@@ -10740,11 +10263,8 @@
       <c r="F159" s="5"/>
       <c r="G159" s="5"/>
       <c r="H159" s="5"/>
-      <c r="I159">
-        <v>33229</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>148</v>
       </c>
@@ -10763,11 +10283,8 @@
       <c r="F160" s="5"/>
       <c r="G160" s="5"/>
       <c r="H160" s="5"/>
-      <c r="I160">
-        <v>5558</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>149</v>
       </c>
@@ -10786,11 +10303,8 @@
       <c r="F161" s="5"/>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
-      <c r="I161">
-        <v>8150</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>150</v>
       </c>
@@ -10809,11 +10323,8 @@
       <c r="F162" s="5"/>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
-      <c r="I162">
-        <v>12087</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>153</v>
       </c>
@@ -10832,11 +10343,8 @@
       <c r="F163" s="5"/>
       <c r="G163" s="5"/>
       <c r="H163" s="5"/>
-      <c r="I163">
-        <v>42179</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>154</v>
       </c>
@@ -10855,11 +10363,8 @@
       <c r="F164" s="5"/>
       <c r="G164" s="5"/>
       <c r="H164" s="5"/>
-      <c r="I164">
-        <v>237856</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>155</v>
       </c>
@@ -10878,11 +10383,8 @@
       <c r="F165" s="5"/>
       <c r="G165" s="5"/>
       <c r="H165" s="5"/>
-      <c r="I165">
-        <v>58442</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>186</v>
       </c>
@@ -10901,11 +10403,8 @@
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
       <c r="H166" s="5"/>
-      <c r="I166">
-        <v>45834</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>188</v>
       </c>
@@ -10924,11 +10423,8 @@
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
       <c r="H167" s="5"/>
-      <c r="I167">
-        <v>26948</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>189</v>
       </c>
@@ -10947,11 +10443,8 @@
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
       <c r="H168" s="5"/>
-      <c r="I168">
-        <v>282854</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>190</v>
       </c>
@@ -10970,11 +10463,8 @@
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
       <c r="H169" s="5"/>
-      <c r="I169">
-        <v>37067</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="170" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>157</v>
       </c>
@@ -10997,11 +10487,8 @@
         <v>29</v>
       </c>
       <c r="H170" s="5"/>
-      <c r="I170">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="171" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>159</v>
       </c>
@@ -11024,11 +10511,8 @@
         <v>29</v>
       </c>
       <c r="H171" s="5"/>
-      <c r="I171">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>160</v>
       </c>
@@ -11051,11 +10535,8 @@
         <v>29</v>
       </c>
       <c r="H172" s="5"/>
-      <c r="I172">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="173" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>161</v>
       </c>
@@ -11078,11 +10559,8 @@
         <v>29</v>
       </c>
       <c r="H173" s="5"/>
-      <c r="I173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="174" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>162</v>
       </c>
@@ -11105,11 +10583,8 @@
         <v>29</v>
       </c>
       <c r="H174" s="5"/>
-      <c r="I174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="175" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>163</v>
       </c>
@@ -11132,11 +10607,8 @@
         <v>29</v>
       </c>
       <c r="H175" s="5"/>
-      <c r="I175">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>164</v>
       </c>
@@ -11159,11 +10631,8 @@
         <v>29</v>
       </c>
       <c r="H176" s="5"/>
-      <c r="I176">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>165</v>
       </c>
@@ -11186,11 +10655,8 @@
         <v>29</v>
       </c>
       <c r="H177" s="5"/>
-      <c r="I177">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>166</v>
       </c>
@@ -11213,11 +10679,8 @@
         <v>29</v>
       </c>
       <c r="H178" s="5"/>
-      <c r="I178">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>167</v>
       </c>
@@ -11240,11 +10703,8 @@
         <v>29</v>
       </c>
       <c r="H179" s="5"/>
-      <c r="I179">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>168</v>
       </c>
@@ -11267,11 +10727,8 @@
         <v>29</v>
       </c>
       <c r="H180" s="5"/>
-      <c r="I180">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="181" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>169</v>
       </c>
@@ -11294,11 +10751,8 @@
         <v>29</v>
       </c>
       <c r="H181" s="5"/>
-      <c r="I181">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="182" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>170</v>
       </c>
@@ -11321,11 +10775,8 @@
         <v>29</v>
       </c>
       <c r="H182" s="5"/>
-      <c r="I182">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>171</v>
       </c>
@@ -11348,11 +10799,8 @@
         <v>29</v>
       </c>
       <c r="H183" s="5"/>
-      <c r="I183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>172</v>
       </c>
@@ -11375,11 +10823,8 @@
         <v>29</v>
       </c>
       <c r="H184" s="5"/>
-      <c r="I184">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>173</v>
       </c>
@@ -11402,11 +10847,8 @@
         <v>29</v>
       </c>
       <c r="H185" s="5"/>
-      <c r="I185">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>174</v>
       </c>
@@ -11429,11 +10871,8 @@
         <v>29</v>
       </c>
       <c r="H186" s="5"/>
-      <c r="I186">
-        <v>5830</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>175</v>
       </c>
@@ -11456,11 +10895,8 @@
         <v>29</v>
       </c>
       <c r="H187" s="5"/>
-      <c r="I187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>179</v>
       </c>
@@ -11485,11 +10921,8 @@
       <c r="H188" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="I188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>176</v>
       </c>
@@ -11512,13 +10945,10 @@
         <v>29</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="I189">
-        <v>11867</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>177</v>
       </c>
@@ -11541,13 +10971,10 @@
         <v>29</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="I190">
-        <v>14409</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>178</v>
       </c>
@@ -11570,9 +10997,6 @@
         <v>29</v>
       </c>
       <c r="H191" s="5"/>
-      <c r="I191">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
